--- a/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:09:08+00:00</t>
+    <t>2026-09-15T14:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:24:26+00:00</t>
+    <t>2026-09-15T15:11:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:11:37+00:00</t>
+    <t>2026-09-16T10:02:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T10:02:19+00:00</t>
+    <t>2026-09-22T13:51:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T13:51:41+00:00</t>
+    <t>2026-09-22T15:20:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T15:20:18+00:00</t>
+    <t>2026-09-22T17:31:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
